--- a/KSA VAT Workbook Sample.xlsx
+++ b/KSA VAT Workbook Sample.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1098047bab615bc4/Desktop/Pessimism/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahmed\Music\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{B290042E-8A2A-4AFD-9DD9-9CA79CF0C91E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCDEC7FA-85CA-4E5F-B52E-F5313DBDD69D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49AD5A77-C09C-44D5-B7DC-78C9FA1D269E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,20 +41,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="165">
   <si>
     <t>VAT Return Summary (Sample)</t>
   </si>
   <si>
-    <t>Total Output VAT (SAR)</t>
-  </si>
-  <si>
-    <t>Total Input VAT - Claimable (SAR)</t>
-  </si>
-  <si>
-    <t>Net VAT Payable (Output - Input) (SAR)</t>
-  </si>
-  <si>
     <t>Ensure all invoices are compliant. Non-compliant purchases are excluded from Input VAT.</t>
   </si>
   <si>
@@ -235,9 +226,6 @@
     <t>Has this invoice been included/excluded correctly in VAT return?</t>
   </si>
   <si>
-    <t>Amount</t>
-  </si>
-  <si>
     <t>S-003</t>
   </si>
   <si>
@@ -457,24 +445,6 @@
     <t>Invalid Input Claim - Missing QR Code</t>
   </si>
   <si>
-    <t>Amount2</t>
-  </si>
-  <si>
-    <t>Taxable Supplies - Standard Rated</t>
-  </si>
-  <si>
-    <t>Taxable Supplies - Zero Rated</t>
-  </si>
-  <si>
-    <t>Taxable Purchases - Standard Rated</t>
-  </si>
-  <si>
-    <t>Taxable Purchases - Zero Rated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax </t>
-  </si>
-  <si>
     <t>EXCLUSIONS FROM INPUT VAT CLAIM</t>
   </si>
   <si>
@@ -500,17 +470,94 @@
   </si>
   <si>
     <t>Valid</t>
+  </si>
+  <si>
+    <t>Net</t>
+  </si>
+  <si>
+    <t>Net VAT Due (or claim)</t>
+  </si>
+  <si>
+    <t>VAT credit carried forward from 
+previous period</t>
+  </si>
+  <si>
+    <t>corrections from previous period
+(between SAR +-5000)</t>
+  </si>
+  <si>
+    <t>Total VAT due for current period</t>
+  </si>
+  <si>
+    <t>Total purchases</t>
+  </si>
+  <si>
+    <t>Exempt purchases</t>
+  </si>
+  <si>
+    <t>Zero Rated purchases</t>
+  </si>
+  <si>
+    <t>imports subject to VAT accounted for
+through reverse charge mechanism
+5%</t>
+  </si>
+  <si>
+    <t>imports subject to VAT accounted for
+through reverse charge mechanism
+15%</t>
+  </si>
+  <si>
+    <t>Imports subject to VAT paid at 
+Customs 5%</t>
+  </si>
+  <si>
+    <t>Standard rate domestic purchases 5%</t>
+  </si>
+  <si>
+    <t>Standard rate domestic purchases 15%</t>
+  </si>
+  <si>
+    <t>Total Sales</t>
+  </si>
+  <si>
+    <t>Exempt sales</t>
+  </si>
+  <si>
+    <t>Exports</t>
+  </si>
+  <si>
+    <t>Zero rate domestic sale</t>
+  </si>
+  <si>
+    <t>Private healthcare/private education/first house sale to citizen</t>
+  </si>
+  <si>
+    <t>Standard rate sales 5%</t>
+  </si>
+  <si>
+    <t>Standard rate sales 15%</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Imports subject to VAT paid at
+Customs 15%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;?_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.00000000000_-;\-* #,##0.00000000000_-;_-* &quot;-&quot;?_-;_-@_-"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -540,16 +587,43 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -679,27 +753,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -742,10 +801,20 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="43" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -754,23 +823,7 @@
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="71">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="65">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1239,6 +1292,22 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -1832,116 +1901,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="35" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1953,6 +1912,102 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>120651</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C1D0EBF-34EC-052D-22E8-9E6AA6BCD890}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="6896100" y="920750"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304800" cy="304095"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D90A78F1-A7C9-4BE1-8099-63CE6E38C919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7203722" y="0"/>
+          <a:ext cx="304800" cy="304095"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1972,24 +2027,16 @@
 </FeaturePropertyBags>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E87E75B-BD8D-4BA3-9FD0-990816BC85AB}" name="Table1" displayName="Table1" ref="A1:D10" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" headerRowCellStyle="Comma" dataCellStyle="Comma">
-  <autoFilter ref="A1:D10" xr:uid="{7E87E75B-BD8D-4BA3-9FD0-990816BC85AB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{2883B8EA-6EC5-49C7-A6A3-6D8798EB8CD6}" name="Table4" displayName="Table4" ref="A2:D22" totalsRowShown="0">
+  <autoFilter ref="A2:D22" xr:uid="{2883B8EA-6EC5-49C7-A6A3-6D8798EB8CD6}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{9F62D12D-6F39-468F-8500-62466446CB5B}" name="VAT Return Summary (Sample)" dataDxfId="68" dataCellStyle="Comma"/>
-    <tableColumn id="3" xr3:uid="{9BD35229-888A-4DCF-AADA-A3278B8C0639}" name="Amount" dataDxfId="67" dataCellStyle="Comma">
-      <calculatedColumnFormula>'Output VAT Schedule'!D1</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="4" xr3:uid="{4B41B96B-FBE0-4DEC-8992-7BCEDDC84B40}" name="Tax " dataDxfId="66" dataCellStyle="Comma">
-      <calculatedColumnFormula>'Output VAT Schedule'!C1</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{9DBEEAC8-55A9-49A5-93FA-164A403DB08E}" name="Amount2" dataDxfId="65" dataCellStyle="Comma"/>
+    <tableColumn id="1" xr3:uid="{87F8D842-FE49-46DA-8370-32B38C02F2BA}" name="#"/>
+    <tableColumn id="2" xr3:uid="{D54FA39C-C117-47FC-9FFD-740E3448F55C}" name="Description"/>
+    <tableColumn id="3" xr3:uid="{561A2153-FA33-48C2-9E7B-853FCFC9435C}" name="Net"/>
+    <tableColumn id="4" xr3:uid="{D9A34C13-947B-4FA9-89C8-098D9FDB3BE3}" name="VAT"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2066,20 +2113,20 @@
     </tableColumn>
     <tableColumn id="11" xr3:uid="{8EB8DC3B-20DE-4581-AC98-9CC426B66573}" name="Invoice Type" dataDxfId="33"/>
     <tableColumn id="12" xr3:uid="{5CF24959-ED0C-46CC-8B39-3137625BF755}" name="QR Code" dataDxfId="32"/>
-    <tableColumn id="14" xr3:uid="{86AC1A4A-BA2F-4AA4-BAF6-92E59C203E2C}" name="Compliant?" dataDxfId="0"/>
+    <tableColumn id="14" xr3:uid="{86AC1A4A-BA2F-4AA4-BAF6-92E59C203E2C}" name="Compliant?" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1B31C323-A024-41A2-9A8E-65552ACC01BF}" name="Table8" displayName="Table8" ref="A1:D3" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29" totalsRowBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{1B31C323-A024-41A2-9A8E-65552ACC01BF}" name="Table8" displayName="Table8" ref="A1:D3" totalsRowShown="0" headerRowDxfId="30" headerRowBorderDxfId="29" tableBorderDxfId="28" totalsRowBorderDxfId="27">
   <autoFilter ref="A1:D3" xr:uid="{1B31C323-A024-41A2-9A8E-65552ACC01BF}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{B4C74DD9-F0D8-409B-AFEC-16F4E6BF70B4}" name="Description" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{FE169538-B88A-4570-A13D-FFA67F3C0719}" name="Taxable Amount" dataDxfId="26" dataCellStyle="Comma"/>
-    <tableColumn id="4" xr3:uid="{B86D7912-0C7D-4728-A32E-0DA0C2B032E4}" name="VAT Amount" dataDxfId="25" dataCellStyle="Comma"/>
-    <tableColumn id="5" xr3:uid="{FE16FA00-0054-409E-ACC8-7BE36DE7C807}" name="Total" dataDxfId="24" dataCellStyle="Comma">
+    <tableColumn id="1" xr3:uid="{B4C74DD9-F0D8-409B-AFEC-16F4E6BF70B4}" name="Description" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{FE169538-B88A-4570-A13D-FFA67F3C0719}" name="Taxable Amount" dataDxfId="25" dataCellStyle="Comma"/>
+    <tableColumn id="4" xr3:uid="{B86D7912-0C7D-4728-A32E-0DA0C2B032E4}" name="VAT Amount" dataDxfId="24" dataCellStyle="Comma"/>
+    <tableColumn id="5" xr3:uid="{FE16FA00-0054-409E-ACC8-7BE36DE7C807}" name="Total" dataDxfId="23" dataCellStyle="Comma">
       <calculatedColumnFormula>SUM(Table8[[#This Row],[VAT Amount]],Table8[[#This Row],[Taxable Amount]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2088,17 +2135,17 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00431ED2-2E07-4892-A596-AC43EAB66DC7}" name="Table11" displayName="Table11" ref="A2:H3" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="22" tableBorderDxfId="21" totalsRowBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00431ED2-2E07-4892-A596-AC43EAB66DC7}" name="Table11" displayName="Table11" ref="A2:H3" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="A2:H3" xr:uid="{00431ED2-2E07-4892-A596-AC43EAB66DC7}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{136F368A-BF6F-4FA8-8A1F-B1AFF5DD62DD}" name="Invoice Number" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{D831D858-50D1-46AE-9257-A4E920997996}" name="Invoice Date" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{9A10841E-D215-44F4-AAA1-A7919817876E}" name="Supplier Name" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{DF2CE9C1-519E-4DBD-9969-D1B1881B1728}" name="Item Description" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{5E804317-3890-466C-B99D-B8E920BE9280}" name="Description" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{96E857E1-1F14-47CB-8726-0C9D91BDDC50}" name="Quantity" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{D3DE2BB7-07F6-4A30-93C9-762AB995D2D3}" name="Unit Price (SAR)" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{154619D4-D9DA-4F58-8711-327DF9A3E445}" name="Total Excl. VAT (SAR)" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{136F368A-BF6F-4FA8-8A1F-B1AFF5DD62DD}" name="Invoice Number" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{D831D858-50D1-46AE-9257-A4E920997996}" name="Invoice Date" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{9A10841E-D215-44F4-AAA1-A7919817876E}" name="Supplier Name" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{DF2CE9C1-519E-4DBD-9969-D1B1881B1728}" name="Item Description" dataDxfId="15"/>
+    <tableColumn id="14" xr3:uid="{5E804317-3890-466C-B99D-B8E920BE9280}" name="Description" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{96E857E1-1F14-47CB-8726-0C9D91BDDC50}" name="Quantity" dataDxfId="13"/>
+    <tableColumn id="6" xr3:uid="{D3DE2BB7-07F6-4A30-93C9-762AB995D2D3}" name="Unit Price (SAR)" dataDxfId="12"/>
+    <tableColumn id="7" xr3:uid="{154619D4-D9DA-4F58-8711-327DF9A3E445}" name="Total Excl. VAT (SAR)" dataDxfId="11">
       <calculatedColumnFormula>G3*F3</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2107,7 +2154,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{A7E9A8FA-069D-4E90-8253-FBA702E2C7C0}" name="Table7" displayName="Table7" ref="A1:E4" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{A7E9A8FA-069D-4E90-8253-FBA702E2C7C0}" name="Table7" displayName="Table7" ref="A1:E4" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:E4" xr:uid="{A7E9A8FA-069D-4E90-8253-FBA702E2C7C0}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{FA0E830D-509C-4458-8D46-163D6432DF7C}" name="Date"/>
@@ -2121,13 +2168,13 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E6E58734-0022-4818-8311-AF3177552DB1}" name="Table3" displayName="Table3" ref="A1:D9" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E6E58734-0022-4818-8311-AF3177552DB1}" name="Table3" displayName="Table3" ref="A1:D9" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:D9" xr:uid="{E6E58734-0022-4818-8311-AF3177552DB1}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{CAB5B1A6-79DE-42C4-95B7-B1D928CB4812}" name="Check Item" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{E8838550-6E07-4043-9BBA-94244DD2F09F}" name="Description" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{14302CD6-C15D-409E-9803-EB280BB70C2C}" name="Status (Yes/No)" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{FAB6FBEB-A2DD-45FA-ACA8-1C14F39B4A96}" name="Comments" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{CAB5B1A6-79DE-42C4-95B7-B1D928CB4812}" name="Check Item" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{E8838550-6E07-4043-9BBA-94244DD2F09F}" name="Description" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{14302CD6-C15D-409E-9803-EB280BB70C2C}" name="Status (Yes/No)" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{FAB6FBEB-A2DD-45FA-ACA8-1C14F39B4A96}" name="Comments" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleDark9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2418,170 +2465,280 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.54296875" customWidth="1"/>
-    <col min="2" max="3" width="10.7265625" customWidth="1"/>
-    <col min="4" max="4" width="10.1796875" customWidth="1"/>
-    <col min="5" max="7" width="33.54296875" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.54296875" customWidth="1"/>
+    <col min="3" max="4" width="10.7265625" customWidth="1"/>
+    <col min="5" max="5" width="10.1796875" customWidth="1"/>
+    <col min="6" max="8" width="33.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="39"/>
+      <c r="D1" s="39"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="D2" s="30" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="30">
-        <f>D3+D4</f>
-        <v>6345</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B3" s="1">
+      <c r="B3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="12">
         <f>'Output VAT Schedule'!D2</f>
         <v>42300</v>
       </c>
-      <c r="C3" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="D3" s="1">
-        <f>Table1[[#This Row],[Amount]]*Table1[[#This Row],[Tax ]]</f>
+      <c r="D3" s="12">
+        <f>'Output VAT Schedule'!C2</f>
         <v>6345</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="B4" s="1">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="31">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="12">
         <f>'Output VAT Schedule'!D3</f>
         <v>9000</v>
       </c>
-      <c r="C4" s="32">
+      <c r="D7" s="12">
+        <f>'Output VAT Schedule'!C3</f>
         <v>0</v>
       </c>
-      <c r="D4" s="1">
-        <f>Table1[[#This Row],[Amount]]*Table1[[#This Row],[Tax ]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="30">
-        <f>D7+D8</f>
-        <v>4941.5999999999995</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="1">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="33">
+        <f>SUM(C3:C8)</f>
+        <v>51300</v>
+      </c>
+      <c r="D9" s="33">
+        <f>SUM(D3:D8)</f>
+        <v>6345</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C10" s="12">
         <f>'Input VAT Schedule'!B2</f>
         <v>32944</v>
       </c>
-      <c r="C7" s="32">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="1">
-        <f>Table1[[#This Row],[Amount]]*Table1[[#This Row],[Tax ]]</f>
-        <v>4941.5999999999995</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="1">
-        <f>'Input VAT Schedule'!B3</f>
-        <v>2000</v>
-      </c>
-      <c r="C8" s="32">
-        <v>0</v>
-      </c>
-      <c r="D8" s="1">
-        <f>Table1[[#This Row],[Amount]]*Table1[[#This Row],[Tax ]]</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1">
-        <f>'Output VAT Schedule'!D8</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="1">
-        <f>'Output VAT Schedule'!C8</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="31">
-        <f>'Output VAT Schedule'!D9</f>
-        <v>0</v>
-      </c>
-      <c r="C10" s="31">
-        <f>'Output VAT Schedule'!C9</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="33">
-        <f>D2 - D6</f>
-        <v>1403.4000000000005</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="D10" s="12">
+        <f>'Input VAT Schedule'!C2</f>
+        <v>4941.6000000000004</v>
+      </c>
+      <c r="E10" s="37"/>
+      <c r="H10" s="38"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>7.1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>8.1</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>9</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="H14" s="12"/>
+    </row>
+    <row r="15" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>9.1</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>10</v>
+      </c>
+      <c r="B16" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>11</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>12</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="33">
+        <f>SUM(C10:C17)</f>
+        <v>32944</v>
+      </c>
+      <c r="D18" s="33">
+        <f>SUM(D10:D17)</f>
+        <v>4941.6000000000004</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>13</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="C19" s="36">
+        <f>C9-C18</f>
+        <v>18356</v>
+      </c>
+      <c r="D19" s="36">
+        <f>ROUND(D9-D18,2)</f>
+        <v>1403.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>14</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>15</v>
+      </c>
+      <c r="B21" s="32" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>146</v>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>16</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="C22" s="36">
+        <f>C19</f>
+        <v>18356</v>
+      </c>
+      <c r="D22" s="36">
+        <f>D19</f>
+        <v>1403.4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B25" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B26" t="s">
+        <v>136</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -2596,37 +2753,37 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -2659,10 +2816,10 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B1" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1"/>
     </row>
@@ -2674,60 +2831,60 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="G3" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="I3" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="J3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="K3" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="L3" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="M3" s="20" t="s">
         <v>18</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="20" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F4" s="6">
         <v>20</v>
@@ -2751,27 +2908,27 @@
         <v>690</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D5" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="F5" s="6">
         <v>25</v>
@@ -2795,27 +2952,27 @@
         <v>1437.5</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="F6" s="6">
         <v>80</v>
@@ -2839,27 +2996,27 @@
         <v>1380</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F7" s="6">
         <v>50</v>
@@ -2883,27 +3040,27 @@
         <v>1725</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F8" s="6">
         <v>100</v>
@@ -2927,27 +3084,27 @@
         <v>3000</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F9" s="6">
         <v>250</v>
@@ -2971,27 +3128,27 @@
         <v>5750</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>79</v>
-      </c>
       <c r="D10" s="14" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F10" s="6">
         <v>500</v>
@@ -3015,27 +3172,27 @@
         <v>5750</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F11" s="6">
         <v>800</v>
@@ -3059,27 +3216,27 @@
         <v>9200</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="D12" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F12" s="6">
         <v>200</v>
@@ -3102,27 +3259,27 @@
         <v>6000</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F13" s="6">
         <v>1000</v>
@@ -3146,27 +3303,27 @@
         <v>11500</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>104</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F14" s="6">
         <v>250</v>
@@ -3190,27 +3347,27 @@
         <v>4312.5</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F15" s="9">
         <v>400</v>
@@ -3234,10 +3391,10 @@
         <v>6900</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3261,21 +3418,21 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" s="12">
         <f>C2+D2</f>
@@ -3293,7 +3450,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B3" s="12">
         <f>C3+D3</f>
@@ -3354,65 +3511,65 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="B1" s="16" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C1" s="17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="M3" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B4" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="E4" s="6">
         <v>60</v>
@@ -3436,27 +3593,27 @@
         <v>690</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E5" s="6">
         <v>100</v>
@@ -3479,27 +3636,27 @@
         <v>2000</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="E6" s="6">
         <v>3200</v>
@@ -3523,27 +3680,27 @@
         <v>1545.6</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E7" s="6">
         <v>1000</v>
@@ -3567,27 +3724,27 @@
         <v>13800</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E8" s="6">
         <v>100</v>
@@ -3611,27 +3768,27 @@
         <v>9200</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>121</v>
-      </c>
       <c r="C9" s="6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E9" s="6">
         <v>250</v>
@@ -3655,27 +3812,27 @@
         <v>5750</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="21" t="s">
-        <v>122</v>
-      </c>
       <c r="C10" s="9" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E10" s="9">
         <v>500</v>
@@ -3699,13 +3856,13 @@
         <v>6900</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3734,29 +3891,29 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D1" s="24" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B2" s="25">
         <f>SUMIFS(Purchases!G:G, Purchases!M:M, "Yes")</f>
         <v>32944</v>
       </c>
       <c r="C2" s="25">
-        <f>Table8[[#This Row],[Taxable Amount]]*0.15</f>
-        <v>4941.5999999999995</v>
+        <f>ROUND(Table8[[#This Row],[Taxable Amount]]*0.15,2)</f>
+        <v>4941.6000000000004</v>
       </c>
       <c r="D2" s="26">
         <f>SUM(Table8[[#This Row],[VAT Amount]],Table8[[#This Row],[Taxable Amount]])</f>
@@ -3765,7 +3922,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B3" s="25">
         <f>SUMIFS(Purchases!G:G, Purchases!M:M, "No")</f>
@@ -3803,58 +3960,58 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A1" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
+      <c r="A1" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="8" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F3" s="9">
         <v>100</v>
@@ -3892,27 +4049,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="22" t="s">
         <v>35</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1">
         <v>0</v>
@@ -3922,43 +4079,43 @@
         <v>6345</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" t="s">
         <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>42</v>
       </c>
       <c r="C3" s="1">
         <f>'Input VAT Schedule'!C2</f>
-        <v>4941.5999999999995</v>
+        <v>4941.6000000000004</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
       </c>
       <c r="D4" s="1">
-        <f>D2-C3</f>
-        <v>1403.4000000000005</v>
+        <f>ROUND(D2-C3,2)</f>
+        <v>1403.4</v>
       </c>
       <c r="E4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -3982,128 +4139,128 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C2" s="11" t="b">
         <v>1</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C3" s="11" t="b">
         <v>1</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C4" s="11" t="b">
         <v>1</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" s="11" t="b">
         <v>0</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" s="11" t="b">
         <v>1</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C7" s="11" t="b">
         <v>1</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C8" s="11" t="b">
         <v>1</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C9" s="11" t="b">
         <v>1</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
